--- a/Result/profitability/5519.xlsx
+++ b/Result/profitability/5519.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0275</v>
+        <v>1.03125</v>
       </c>
       <c r="N2" t="n">
-        <v>26.1975</v>
+        <v>27.03125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03625</v>
+        <v>0.8075</v>
       </c>
       <c r="N3" t="n">
-        <v>24.48375</v>
+        <v>23.925</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.835</v>
+        <v>0.79125</v>
       </c>
       <c r="N4" t="n">
-        <v>21.685</v>
+        <v>21.58625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8324999999999999</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>19.04375</v>
+        <v>19.475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.81125</v>
+        <v>0.3975</v>
       </c>
       <c r="N6" t="n">
-        <v>16.78875</v>
+        <v>15.6575</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.375</v>
+        <v>0.31875</v>
       </c>
       <c r="N7" t="n">
-        <v>13.1025</v>
+        <v>12.10625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.31125</v>
+        <v>0.265</v>
       </c>
       <c r="N8" t="n">
-        <v>9.793749999999999</v>
+        <v>8.983750000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>452</v>
+      </c>
+      <c r="D75" t="n">
+        <v>333</v>
+      </c>
+      <c r="E75" t="n">
+        <v>119</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>62</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9974999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6379310344827587</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1976815131177547</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.08695652173913049</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.449999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1509846827133479</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
